--- a/referral_form_templates/041_rehabilitation_center_referral_form--referral_form_templates.xlsx
+++ b/referral_form_templates/041_rehabilitation_center_referral_form--referral_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'self'}</t>
+          <t>self</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Self'}</t>
+          <t>Self</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Family member'}</t>
+          <t>Family member</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'insurance_company'}</t>
+          <t>insurance_company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Insurance company'}</t>
+          <t>Insurance company</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'asian'}</t>
+          <t>asian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Asian'}</t>
+          <t>Asian</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'asian_or_pacific_islander'}</t>
+          <t>asian_or_pacific_islander</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Asian or Pacific Islander'}</t>
+          <t>Asian or Pacific Islander</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'White'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'nurse_practitioner'}</t>
+          <t>nurse_practitioner</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Nurse Practitioner'}</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
